--- a/output/pdf_financials_xlsx/BLO.xlsx
+++ b/output/pdf_financials_xlsx/BLO.xlsx
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>7.763969</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>8.632443</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>10.530201</v>
       </c>
     </row>
     <row r="93">
@@ -3142,7 +3142,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -3297,7 +3301,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>7.763969</v>
       </c>

--- a/output/pdf_financials_xlsx/BLO.xlsx
+++ b/output/pdf_financials_xlsx/BLO.xlsx
@@ -577,10 +577,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2.028093</v>
+        <v>2.277643</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2.17432</v>
+        <v>3.300691</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>3.202744</v>
@@ -593,10 +593,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-2.028093</v>
+        <v>-2.277643</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-2.17432</v>
+        <v>-3.300691</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-3.202744</v>
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.176205</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.196526</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.104192</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.138116</v>
+        <v>-2.314321</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.126607</v>
+        <v>-3.323133</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.686316</v>
+        <v>-4.790508</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.01183</v>
+        <v>-2.188035</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.973372</v>
+        <v>-3.169898</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.517796</v>
+        <v>-4.621988</v>
       </c>
     </row>
     <row r="30">
@@ -2419,13 +2419,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.124118</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.143527</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.153719</v>
       </c>
     </row>
     <row r="125">
@@ -2435,13 +2435,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.124118</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.143527</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.153719</v>
       </c>
     </row>
     <row r="126">
@@ -3795,7 +3795,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>-0.124118</v>
       </c>
@@ -4496,7 +4500,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
@@ -4527,7 +4531,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
@@ -5089,7 +5093,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">

--- a/output/pdf_financials_xlsx/BLO.xlsx
+++ b/output/pdf_financials_xlsx/BLO.xlsx
@@ -2211,13 +2211,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.028649</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.029149</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.024414</v>
       </c>
     </row>
     <row r="112">
@@ -2585,13 +2585,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.028649</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.029149</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.024414</v>
       </c>
     </row>
     <row r="135">
@@ -2601,13 +2601,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.966453</v>
+        <v>-1.995102</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-2.08066</v>
+        <v>-2.109809</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.835551</v>
+        <v>-1.859965</v>
       </c>
     </row>
   </sheetData>
@@ -3706,7 +3706,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>-0.028649</v>
       </c>
